--- a/masters/v23.6/masterz-text-v126.xlsx
+++ b/masters/v23.6/masterz-text-v126.xlsx
@@ -3892,265 +3892,250 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.sequence</t>
+          <t xml:space="preserve">event.changeLook</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAP EACH ONE</t>
+          <t xml:space="preserve">REMEMBER THE ROOM</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.match</t>
+          <t xml:space="preserve">event.changeLookWhere</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAG EACH ITEM TO ITS PLACE</t>
+          <t xml:space="preserve">Nothing has changed yet</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.matchOk</t>
+          <t xml:space="preserve">event.sequence</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCHED</t>
+          <t xml:space="preserve">TAP EACH ONE</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.matchBad</t>
+          <t xml:space="preserve">event.match</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">WRONG ITEM</t>
+          <t xml:space="preserve">DRAG EACH ITEM TO ITS PLACE</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.hit</t>
+          <t xml:space="preserve">event.matchOk</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOOD</t>
+          <t xml:space="preserve">MATCHED</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.miss</t>
+          <t xml:space="preserve">event.matchBad</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">MISSED</t>
+          <t xml:space="preserve">WRONG ITEM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.perfect</t>
+          <t xml:space="preserve">event.hit</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERFECT</t>
+          <t xml:space="preserve">GOOD</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.great</t>
+          <t xml:space="preserve">event.miss</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXCELLENT</t>
+          <t xml:space="preserve">MISSED</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.good</t>
+          <t xml:space="preserve">event.perfect</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOOD TIMING</t>
+          <t xml:space="preserve">PERFECT</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.slight</t>
+          <t xml:space="preserve">event.great</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLIGHT MISS</t>
+          <t xml:space="preserve">EXCELLENT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.missed</t>
+          <t xml:space="preserve">event.good</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">MISSED — SANITY LOST</t>
+          <t xml:space="preserve">GOOD TIMING</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.broken</t>
+          <t xml:space="preserve">event.slight</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOO LATE — SANITY LOST</t>
+          <t xml:space="preserve">SLIGHT MISS</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.start</t>
+          <t xml:space="preserve">event.missed</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">START</t>
+          <t xml:space="preserve">MISSED — SANITY LOST</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">event.ready</t>
+          <t xml:space="preserve">event.broken</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIEFING</t>
+          <t xml:space="preserve">TOO LATE — SANITY LOST</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">card.conduct</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outcome + teaching card — under the stat rows</t>
+          <t xml:space="preserve">event.start</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you did</t>
+          <t xml:space="preserve">START</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">card.ward</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outcome + teaching card — under the stat rows</t>
+          <t xml:space="preserve">event.ready</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amulet −{n}</t>
+          <t xml:space="preserve">BRIEFING</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">decide.clock</t>
+          <t xml:space="preserve">card.conduct</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decision panel</t>
+          <t xml:space="preserve">Outcome + teaching card — under the stat rows</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">It is still coming</t>
+          <t xml:space="preserve">What you did</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.burning</t>
+          <t xml:space="preserve">card.ward</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the world</t>
+          <t xml:space="preserve">Outcome + teaching card — under the stat rows</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Something is burning ahead...</t>
+          <t xml:space="preserve">Amulet −{n}</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.interactKey</t>
+          <t xml:space="preserve">decide.clock</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the world</t>
+          <t xml:space="preserve">Decision panel</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keycap shown on desktop — keep it short</t>
+          <t xml:space="preserve">It is still coming</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.interactKeyTouch</t>
+          <t xml:space="preserve">world.burning</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4160,19 +4145,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keycap shown on phones — keep it short</t>
+          <t xml:space="preserve">Something is burning ahead...</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.interactText</t>
+          <t xml:space="preserve">world.interactKey</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4182,14 +4162,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Examine the pile of hell notes</t>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keycap shown on desktop — keep it short</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.interactTextTouch</t>
+          <t xml:space="preserve">world.interactKeyTouch</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4199,14 +4184,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">the pile of hell notes</t>
+          <t xml:space="preserve">Tap</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keycap shown on phones — keep it short</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.hintWalk</t>
+          <t xml:space="preserve">world.interactText</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4216,14 +4206,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk toward the light</t>
+          <t xml:space="preserve">Examine the pile of hell notes</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.hintPhone</t>
+          <t xml:space="preserve">world.interactTextTouch</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4233,14 +4223,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left thumb walks · right thumb looks</t>
+          <t xml:space="preserve">the pile of hell notes</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.hintMouseTouch</t>
+          <t xml:space="preserve">world.hintWalk</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4250,14 +4240,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">W A S D to walk · move the mouse to look · touch works too</t>
+          <t xml:space="preserve">Walk toward the light</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.hintLocked</t>
+          <t xml:space="preserve">world.hintPhone</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4267,14 +4257,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">W A S D to walk · move the mouse to look</t>
+          <t xml:space="preserve">Left thumb walks · right thumb looks</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.hintEdges</t>
+          <t xml:space="preserve">world.hintMouseTouch</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4284,14 +4274,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">W A S D to walk · move the mouse to look</t>
+          <t xml:space="preserve">W A S D to walk · move the mouse to look · touch works too</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.actHintTouch</t>
+          <t xml:space="preserve">world.hintLocked</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4301,19 +4291,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap the glowing pile</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tail of the hint line, phones</t>
+          <t xml:space="preserve">W A S D to walk · move the mouse to look</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.actHintKey</t>
+          <t xml:space="preserve">world.hintEdges</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4323,19 +4308,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E at the glowing pile</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tail of the hint line, desktop</t>
+          <t xml:space="preserve">W A S D to walk · move the mouse to look</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.actLineTouch</t>
+          <t xml:space="preserve">world.actHintTouch</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4345,19 +4325,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap the glowing pile of notes to look again</t>
+          <t xml:space="preserve">tap the glowing pile</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">After stepping back, phones</t>
+          <t xml:space="preserve">Tail of the hint line, phones</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">world.actLineKey</t>
+          <t xml:space="preserve">world.actHintKey</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4367,104 +4347,114 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Press E at the glowing pile to look again</t>
+          <t xml:space="preserve">E at the glowing pile</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">After stepping back, desktop</t>
+          <t xml:space="preserve">Tail of the hint line, desktop</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">cine.skip</t>
+          <t xml:space="preserve">world.actLineTouch</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cutscenes</t>
+          <t xml:space="preserve">In the world</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip ▸</t>
+          <t xml:space="preserve">Tap the glowing pile of notes to look again</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After stepping back, phones</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">decide.label</t>
+          <t xml:space="preserve">world.actLineKey</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decision panel</t>
+          <t xml:space="preserve">In the world</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decision</t>
+          <t xml:space="preserve">Press E at the glowing pile to look again</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After stepping back, desktop</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">decide.stepBack</t>
+          <t xml:space="preserve">cine.skip</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decision panel</t>
+          <t xml:space="preserve">Cutscenes</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step back ✕</t>
+          <t xml:space="preserve">Skip ▸</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">result.label</t>
+          <t xml:space="preserve">decide.label</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outcome + teaching card</t>
+          <t xml:space="preserve">Decision panel</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outcome</t>
+          <t xml:space="preserve">Decision</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">result.teachingLabel</t>
+          <t xml:space="preserve">decide.stepBack</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outcome + teaching card</t>
+          <t xml:space="preserve">Decision panel</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Z’s teaching</t>
+          <t xml:space="preserve">Step back ✕</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">result.next</t>
+          <t xml:space="preserve">result.label</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4474,48 +4464,48 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue</t>
+          <t xml:space="preserve">Outcome</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">complete.label</t>
+          <t xml:space="preserve">result.teachingLabel</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finished the chapter</t>
+          <t xml:space="preserve">Outcome + teaching card</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Case file complete</t>
+          <t xml:space="preserve">Master Z’s teaching</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">complete.sealed</t>
+          <t xml:space="preserve">result.next</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finished the chapter</t>
+          <t xml:space="preserve">Outcome + teaching card</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sealed</t>
+          <t xml:space="preserve">Continue</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">complete.coreLabel</t>
+          <t xml:space="preserve">complete.label</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4525,14 +4515,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core lesson</t>
+          <t xml:space="preserve">Case file complete</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">complete.again</t>
+          <t xml:space="preserve">complete.sealed</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4542,48 +4532,48 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue</t>
+          <t xml:space="preserve">Sealed</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.label</t>
+          <t xml:space="preserve">complete.coreLabel</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lost your nerve</t>
+          <t xml:space="preserve">Finished the chapter</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Case failed</t>
+          <t xml:space="preserve">Core lesson</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.sealed</t>
+          <t xml:space="preserve">complete.again</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lost your nerve</t>
+          <t xml:space="preserve">Finished the chapter</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lost</t>
+          <t xml:space="preserve">Continue</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.say</t>
+          <t xml:space="preserve">lost.label</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4593,14 +4583,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your sanity has shattered. You've seen what no mind was meant to endure.</t>
+          <t xml:space="preserve">Case failed</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.teachingLabel</t>
+          <t xml:space="preserve">lost.sealed</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4610,14 +4600,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Z’s teaching</t>
+          <t xml:space="preserve">Lost</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.teaching</t>
+          <t xml:space="preserve">lost.say</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,14 +4617,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fear is not the danger. Facing what terrifies you...and doing nothing—is.</t>
+          <t xml:space="preserve">Your sanity has shattered. You've seen what no mind was meant to endure.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">lost.retry</t>
+          <t xml:space="preserve">lost.teachingLabel</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4644,58 +4634,48 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retry</t>
+          <t xml:space="preserve">Master Z’s teaching</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">newgame.heading</t>
+          <t xml:space="preserve">lost.teaching</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starting over — the confirmation</t>
+          <t xml:space="preserve">Lost your nerve</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start a new game?</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shown when the player asks to start over</t>
+          <t xml:space="preserve">Fear is not the danger. Facing what terrifies you...and doing nothing—is.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">newgame.body</t>
+          <t xml:space="preserve">lost.retry</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starting over — the confirmation</t>
+          <t xml:space="preserve">Lost your nerve</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your saved progress will be erased and you will begin again from the first chapter.</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The warning under it</t>
+          <t xml:space="preserve">Retry</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">newgame.yes</t>
+          <t xml:space="preserve">newgame.heading</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4705,19 +4685,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start over</t>
+          <t xml:space="preserve">Start a new game?</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erases the save and starts again</t>
+          <t xml:space="preserve">Shown when the player asks to start over</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">newgame.no</t>
+          <t xml:space="preserve">newgame.body</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4727,63 +4707,63 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep playing</t>
+          <t xml:space="preserve">Your saved progress will be erased and you will begin again from the first chapter.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Backs out and keeps the save</t>
+          <t xml:space="preserve">The warning under it</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.button</t>
+          <t xml:space="preserve">newgame.yes</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pause menu (M, or the gear button)</t>
+          <t xml:space="preserve">Starting over — the confirmation</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menu</t>
+          <t xml:space="preserve">Start over</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">The label beside the gear button, desktop only</t>
+          <t xml:space="preserve">Erases the save and starts again</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.buttonKey</t>
+          <t xml:space="preserve">newgame.no</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pause menu (M, or the gear button)</t>
+          <t xml:space="preserve">Starting over — the confirmation</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">Keep playing</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">The keycap on that label — keep it short</t>
+          <t xml:space="preserve">Backs out and keeps the save</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.heading</t>
+          <t xml:space="preserve">menu.button</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4793,14 +4773,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paused</t>
+          <t xml:space="preserve">Menu</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The label beside the gear button, desktop only</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.resume</t>
+          <t xml:space="preserve">menu.buttonKey</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4810,19 +4795,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Return to the game</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Closes the menu and carries on</t>
+          <t xml:space="preserve">The keycap on that label — keep it short</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.chapters</t>
+          <t xml:space="preserve">menu.heading</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4832,19 +4817,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episodes and chapters</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Opens the chapter selector</t>
+          <t xml:space="preserve">Paused</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">menu.toTitle</t>
+          <t xml:space="preserve">menu.resume</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4854,58 +4834,63 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to the title screen</t>
+          <t xml:space="preserve">Return to the game</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saves where you stand and goes to the title screen</t>
+          <t xml:space="preserve">Closes the menu and carries on</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.heading</t>
+          <t xml:space="preserve">menu.chapters</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chapter selector</t>
+          <t xml:space="preserve">The pause menu (M, or the gear button)</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episodes</t>
+          <t xml:space="preserve">Episodes and chapters</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opens the chapter selector</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.hint</t>
+          <t xml:space="preserve">menu.toTitle</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chapter selector</t>
+          <t xml:space="preserve">The pause menu (M, or the gear button)</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick an episode, then a chapter you have reached, to play it again from its opening.</t>
+          <t xml:space="preserve">Back to the title screen</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">The line under the heading</t>
+          <t xml:space="preserve">Saves where you stand and goes to the title screen</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.locked</t>
+          <t xml:space="preserve">chapters.heading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4915,19 +4900,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not yet reached</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shown in place of a chapter name you have not reached yet</t>
+          <t xml:space="preserve">Episodes</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.close</t>
+          <t xml:space="preserve">chapters.hint</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4937,14 +4917,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close ✕</t>
+          <t xml:space="preserve">Pick an episode, then a chapter you have reached, to play it again from its opening.</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The line under the heading</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.ask</t>
+          <t xml:space="preserve">chapters.locked</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4954,19 +4939,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play {chapter} from its beginning? Your current place in the story will be replaced.</t>
+          <t xml:space="preserve">Not yet reached</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asked before replaying a chapter — {chapter} is filled in for you</t>
+          <t xml:space="preserve">Shown in place of a chapter name you have not reached yet</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.yes</t>
+          <t xml:space="preserve">chapters.close</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4976,19 +4961,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play it</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirms the replay</t>
+          <t xml:space="preserve">Close ✕</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.no</t>
+          <t xml:space="preserve">chapters.ask</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4998,19 +4978,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Play {chapter} from its beginning? Your current place in the story will be replaced.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Backs out to the list</t>
+          <t xml:space="preserve">Asked before replaying a chapter — {chapter} is filled in for you</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.unwritten</t>
+          <t xml:space="preserve">chapters.yes</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5020,19 +5000,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not yet written</t>
+          <t xml:space="preserve">Play it</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shown in place of a chapter that is not written yet</t>
+          <t xml:space="preserve">Confirms the replay</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.preview</t>
+          <t xml:space="preserve">chapters.no</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5042,14 +5022,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the works</t>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backs out to the list</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.episode</t>
+          <t xml:space="preserve">chapters.unwritten</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5059,19 +5044,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode {n}</t>
+          <t xml:space="preserve">Not yet written</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">The name of an episode tab, for screen readers — {n} is filled in for you</t>
+          <t xml:space="preserve">Shown in place of a chapter that is not written yet</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.chapter</t>
+          <t xml:space="preserve">chapters.preview</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5081,19 +5066,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapter {n}</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The label of a chapter that is not written yet — {n} is filled in for you</t>
+          <t xml:space="preserve">In the works</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.inProgress</t>
+          <t xml:space="preserve">chapters.episode</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5103,19 +5083,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t xml:space="preserve">In progress</t>
+          <t xml:space="preserve">Episode {n}</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">The word beside a chapter you have reached but not finished, and under an episode you are partway through</t>
+          <t xml:space="preserve">The name of an episode tab, for screen readers — {n} is filled in for you</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.here</t>
+          <t xml:space="preserve">chapters.chapter</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5125,19 +5105,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t xml:space="preserve">You are here</t>
+          <t xml:space="preserve">Chapter {n}</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">The word beside the chapter you are in right now</t>
+          <t xml:space="preserve">The label of a chapter that is not written yet — {n} is filled in for you</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.progress</t>
+          <t xml:space="preserve">chapters.inProgress</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5147,19 +5127,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t xml:space="preserve">{n} of {m} chapters completed</t>
+          <t xml:space="preserve">In progress</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">The line under the case name in the selector — {n} and {m} are filled in for you</t>
+          <t xml:space="preserve">The word beside a chapter you have reached but not finished, and under an episode you are partway through</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.completed</t>
+          <t xml:space="preserve">chapters.here</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5169,14 +5149,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Completed</t>
+          <t xml:space="preserve">You are here</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The word beside the chapter you are in right now</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapters.play</t>
+          <t xml:space="preserve">chapters.progress</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5186,58 +5171,53 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play ▸</t>
+          <t xml:space="preserve">{n} of {m} chapters completed</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The line under the case name in the selector — {n} and {m} are filled in for you</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.label</t>
+          <t xml:space="preserve">chapters.completed</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t xml:space="preserve">The episode-complete card (v6.3)</t>
+          <t xml:space="preserve">The chapter selector</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode complete</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The small line above the big rank</t>
+          <t xml:space="preserve">Completed</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.stamp</t>
+          <t xml:space="preserve">chapters.play</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t xml:space="preserve">The episode-complete card (v6.3)</t>
+          <t xml:space="preserve">The chapter selector</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Case closed</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The red stamp across the rank — keep it short</t>
+          <t xml:space="preserve">Play ▸</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.scoreLabel</t>
+          <t xml:space="preserve">episode.label</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5247,19 +5227,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode score</t>
+          <t xml:space="preserve">Episode complete</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beside the episode's average score</t>
+          <t xml:space="preserve">The small line above the big rank</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.tallyLabel</t>
+          <t xml:space="preserve">episode.stamp</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5269,19 +5249,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five chapters, tallied</t>
+          <t xml:space="preserve">Case closed</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Above the row of five chapter results</t>
+          <t xml:space="preserve">The red stamp across the rank — keep it short</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.mapLabel</t>
+          <t xml:space="preserve">episode.scoreLabel</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5291,19 +5271,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ten cases</t>
+          <t xml:space="preserve">Episode score</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Above the trail of ten cases</t>
+          <t xml:space="preserve">Beside the episode's average score</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.unlocked</t>
+          <t xml:space="preserve">episode.tallyLabel</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5313,19 +5293,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlocked</t>
+          <t xml:space="preserve">Five chapters, tallied</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">The small flag on the next case in the trail</t>
+          <t xml:space="preserve">Above the row of five chapter results</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.next</t>
+          <t xml:space="preserve">episode.mapLabel</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5335,19 +5315,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next · {episode}</t>
+          <t xml:space="preserve">The ten cases</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the trail when the next case exists — {episode} is filled in for you</t>
+          <t xml:space="preserve">Above the trail of ten cases</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.nextUnwritten</t>
+          <t xml:space="preserve">episode.unlocked</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5357,19 +5337,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t xml:space="preserve">{episode} is unlocked. It is not yet written — come back for it.</t>
+          <t xml:space="preserve">Unlocked</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the trail when the next case is not written yet — {episode} is filled in for you</t>
+          <t xml:space="preserve">The small flag on the next case in the trail</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.allDone</t>
+          <t xml:space="preserve">episode.next</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5379,19 +5359,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every case is closed.</t>
+          <t xml:space="preserve">Next · {episode}</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under the trail after the tenth case</t>
+          <t xml:space="preserve">Under the trail when the next case exists — {episode} is filled in for you</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.continue</t>
+          <t xml:space="preserve">episode.nextUnwritten</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5401,19 +5381,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue</t>
+          <t xml:space="preserve">{episode} is unlocked. It is not yet written — come back for it.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">The button when the next case exists</t>
+          <t xml:space="preserve">Under the trail when the next case is not written yet — {episode} is filled in for you</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">episode.toTitle</t>
+          <t xml:space="preserve">episode.allDone</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5423,63 +5403,63 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to the title screen</t>
+          <t xml:space="preserve">Every case is closed.</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">The button when it does not</t>
+          <t xml:space="preserve">Under the trail after the tenth case</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep1.label</t>
+          <t xml:space="preserve">episode.continue</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">The episodes — the ten case files (v6.0)</t>
+          <t xml:space="preserve">The episode-complete card (v6.3)</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 1</t>
+          <t xml:space="preserve">Continue</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">The line above "Chapter N" on the chapter card, and the heading under the episode tabs</t>
+          <t xml:space="preserve">The button when the next case exists</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep1.title</t>
+          <t xml:space="preserve">episode.toTitle</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t xml:space="preserve">The episodes — the ten case files (v6.0)</t>
+          <t xml:space="preserve">The episode-complete card (v6.3)</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hell Note I Should Never Have Taken</t>
+          <t xml:space="preserve">Back to the title screen</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">The name of the case — shown under the episode tabs in the selector</t>
+          <t xml:space="preserve">The button when it does not</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep2.label</t>
+          <t xml:space="preserve">ep1.label</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5489,7 +5469,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 2</t>
+          <t xml:space="preserve">Episode 1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -5501,7 +5481,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep2.title</t>
+          <t xml:space="preserve">ep1.title</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5511,7 +5491,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 3 AM Shower &amp; The Ghost Cyclist</t>
+          <t xml:space="preserve">The Hell Note I Should Never Have Taken</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -5523,7 +5503,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep3.label</t>
+          <t xml:space="preserve">ep2.label</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5533,7 +5513,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 3</t>
+          <t xml:space="preserve">Episode 2</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -5545,7 +5525,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep3.title</t>
+          <t xml:space="preserve">ep2.title</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5555,7 +5535,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve">How It All Began</t>
+          <t xml:space="preserve">The 3 AM Shower &amp; The Ghost Cyclist</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -5567,7 +5547,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep4.label</t>
+          <t xml:space="preserve">ep3.label</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5577,7 +5557,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 4</t>
+          <t xml:space="preserve">Episode 3</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -5589,7 +5569,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep4.title</t>
+          <t xml:space="preserve">ep3.title</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5599,7 +5579,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Teacher In White</t>
+          <t xml:space="preserve">How It All Began</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -5611,7 +5591,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep5.label</t>
+          <t xml:space="preserve">ep4.label</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5621,7 +5601,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 5</t>
+          <t xml:space="preserve">Episode 4</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -5633,7 +5613,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep5.title</t>
+          <t xml:space="preserve">ep4.title</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5643,7 +5623,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Signal And The Translator</t>
+          <t xml:space="preserve">The Teacher In White</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -5655,7 +5635,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep6.label</t>
+          <t xml:space="preserve">ep5.label</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5665,7 +5645,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 6</t>
+          <t xml:space="preserve">Episode 5</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -5677,7 +5657,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep6.title</t>
+          <t xml:space="preserve">ep5.title</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5687,7 +5667,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Ghost Clinging To Her Back</t>
+          <t xml:space="preserve">The Signal And The Translator</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -5699,7 +5679,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep7.label</t>
+          <t xml:space="preserve">ep6.label</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5709,7 +5689,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 7</t>
+          <t xml:space="preserve">Episode 6</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -5721,7 +5701,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep7.title</t>
+          <t xml:space="preserve">ep6.title</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5731,7 +5711,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritual Disturbance After A Crematorium Visit</t>
+          <t xml:space="preserve">The Ghost Clinging To Her Back</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -5743,7 +5723,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep8.label</t>
+          <t xml:space="preserve">ep7.label</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5753,7 +5733,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 8</t>
+          <t xml:space="preserve">Episode 7</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -5765,7 +5745,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep8.title</t>
+          <t xml:space="preserve">ep7.title</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5775,7 +5755,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Toilet Possession: When Belief Isn't Enough</t>
+          <t xml:space="preserve">Spiritual Disturbance After A Crematorium Visit</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -5787,7 +5767,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep9.label</t>
+          <t xml:space="preserve">ep8.label</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5797,7 +5777,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 9</t>
+          <t xml:space="preserve">Episode 8</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -5809,7 +5789,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep9.title</t>
+          <t xml:space="preserve">ep8.title</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5819,7 +5799,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Corner The Dog Wouldn't Go Near</t>
+          <t xml:space="preserve">The Toilet Possession: When Belief Isn't Enough</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -5831,7 +5811,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep10.label</t>
+          <t xml:space="preserve">ep9.label</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5841,7 +5821,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episode 10</t>
+          <t xml:space="preserve">Episode 9</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -5853,7 +5833,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">ep10.title</t>
+          <t xml:space="preserve">ep9.title</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5863,7 +5843,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Mirror That Wouldn't Stop Banging</t>
+          <t xml:space="preserve">The Corner The Dog Wouldn't Go Near</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -5875,51 +5855,51 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.button</t>
+          <t xml:space="preserve">ep10.label</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel</t>
+          <t xml:space="preserve">The episodes — the ten case files (v6.0)</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory</t>
+          <t xml:space="preserve">Episode 10</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">The label beside the button, desktop only</t>
+          <t xml:space="preserve">The line above "Chapter N" on the chapter card, and the heading under the episode tabs</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.buttonKey</t>
+          <t xml:space="preserve">ep10.title</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel</t>
+          <t xml:space="preserve">The episodes — the ten case files (v6.0)</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">The Mirror That Wouldn't Stop Banging</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">The keycap on that label — keep it short</t>
+          <t xml:space="preserve">The name of the case — shown under the episode tabs in the selector</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.title</t>
+          <t xml:space="preserve">inv.button</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5929,14 +5909,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment</t>
+          <t xml:space="preserve">Inventory</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The label beside the button, desktop only</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.close</t>
+          <t xml:space="preserve">inv.buttonKey</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5946,19 +5931,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close ✕</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">The button that shuts the panel</t>
+          <t xml:space="preserve">The keycap on that label — keep it short</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.worn</t>
+          <t xml:space="preserve">inv.title</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5968,14 +5953,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipped</t>
+          <t xml:space="preserve">Equipment</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.carried</t>
+          <t xml:space="preserve">inv.close</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5985,14 +5970,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag</t>
+          <t xml:space="preserve">Close ✕</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The button that shuts the panel</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.empty</t>
+          <t xml:space="preserve">inv.worn</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -6002,19 +5992,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nothing selected</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shown when no item is selected</t>
+          <t xml:space="preserve">Equipped</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.emptyDesc</t>
+          <t xml:space="preserve">inv.carried</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -6024,19 +6009,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap an item to look at it.</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The line under it</t>
+          <t xml:space="preserve">Bag</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.hintTouch</t>
+          <t xml:space="preserve">inv.empty</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -6046,19 +6026,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap an item, then tap where it goes · double-tap to equip</t>
+          <t xml:space="preserve">Nothing selected</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">The how-to line, phones</t>
+          <t xml:space="preserve">Shown when no item is selected</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.hintDesktop</t>
+          <t xml:space="preserve">inv.emptyDesc</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -6068,19 +6048,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drag items, or click it and click where it goes · double-click to equip · I or Esc closes</t>
+          <t xml:space="preserve">Tap an item to look at it.</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">The how-to line, desktop</t>
+          <t xml:space="preserve">The line under it</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.zoom</t>
+          <t xml:space="preserve">inv.hintTouch</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -6090,19 +6070,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Look closer</t>
+          <t xml:space="preserve">Tap an item, then tap where it goes · double-tap to equip</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read aloud for the magnifying-glass button — never seen</t>
+          <t xml:space="preserve">The how-to line, phones</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.zoomClose</t>
+          <t xml:space="preserve">inv.hintDesktop</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -6112,19 +6092,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close ✕</t>
+          <t xml:space="preserve">Drag items, or click it and click where it goes · double-click to equip · I or Esc closes</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Closes the big item view</t>
+          <t xml:space="preserve">The how-to line, desktop</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.zoomHint</t>
+          <t xml:space="preserve">inv.zoom</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -6134,63 +6114,63 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drag to turn it · pinch or scroll to zoom</t>
+          <t xml:space="preserve">Look closer</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">The how-to line under the big item view</t>
+          <t xml:space="preserve">Read aloud for the magnifying-glass button — never seen</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot.head</t>
+          <t xml:space="preserve">inv.zoomClose</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — slot names</t>
+          <t xml:space="preserve">Equipment panel</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Divine Eyes</t>
+          <t xml:space="preserve">Close ✕</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the figure's head</t>
+          <t xml:space="preserve">Closes the big item view</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot.neck</t>
+          <t xml:space="preserve">inv.zoomHint</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — slot names</t>
+          <t xml:space="preserve">Equipment panel</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amulet</t>
+          <t xml:space="preserve">Drag to turn it · pinch or scroll to zoom</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the figure's neck</t>
+          <t xml:space="preserve">The how-to line under the big item view</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot.body</t>
+          <t xml:space="preserve">slot.head</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -6200,19 +6180,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sak Yant</t>
+          <t xml:space="preserve">Divine Eyes</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">On the figure's torso</t>
+          <t xml:space="preserve">On the figure's head</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot.hand</t>
+          <t xml:space="preserve">slot.neck</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -6222,58 +6202,63 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hand</t>
+          <t xml:space="preserve">Amulet</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">His hand — the torch goes here</t>
+          <t xml:space="preserve">On the figure's neck</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.torch.name</t>
+          <t xml:space="preserve">slot.body</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — the items</t>
+          <t xml:space="preserve">Equipment panel — slot names</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torch</t>
+          <t xml:space="preserve">Sak Yant</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the figure's torso</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.torch.desc</t>
+          <t xml:space="preserve">slot.hand</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — the items</t>
+          <t xml:space="preserve">Equipment panel — slot names</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Army issue. A wide, hard beam and a heavy switch.</t>
+          <t xml:space="preserve">Hand</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shown beside the torch in the equipment panel</t>
+          <t xml:space="preserve">His hand — the torch goes here</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.rifle.name</t>
+          <t xml:space="preserve">item.torch.name</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -6283,14 +6268,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rifle</t>
+          <t xml:space="preserve">Torch</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.rifle.desc</t>
+          <t xml:space="preserve">item.torch.desc</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -6300,14 +6285,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Army issue. Signed out to you by serial number, and signed back in the same way.</t>
+          <t xml:space="preserve">Army issue. A wide, hard beam and a heavy switch.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown beside the torch in the equipment panel</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.amulet.name</t>
+          <t xml:space="preserve">item.rifle.name</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6317,14 +6307,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP Phiboon Second Batch Rian Amulet (Small)</t>
+          <t xml:space="preserve">Rifle</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.amulet.desc</t>
+          <t xml:space="preserve">item.rifle.desc</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6334,14 +6324,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Powerful against danger, negative energies, black magic and bad spirits. Provides +15 protection against sanity damage. Also boosts Metta Mahaniyom. Made by the powerful Luang Pu PhiBoon (PhiBoon Sae Tan), born during the reign of King Rama 4 in Thailand.</t>
+          <t xml:space="preserve">Army issue. Signed out to you by serial number, and signed back in the same way.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.timkp.name</t>
+          <t xml:space="preserve">item.amulet.name</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6351,14 +6341,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t xml:space="preserve">LP Tim Khun Paen Lode Series, Wat Lahanrai</t>
+          <t xml:space="preserve">LP Phiboon Second Batch Rian Amulet (Small)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.timkp.desc</t>
+          <t xml:space="preserve">item.amulet.desc</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6368,14 +6358,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Made by the renowned LP Tim Issariko of Wat Lahanrai, this amulet is imbued with the powers from its Phong Prai Kuman powder, granting the wearer prosperity and enhancing charm. Reduce all kinds of damage from minigame events by 50%.</t>
+          <t xml:space="preserve">Powerful against danger, negative energies, black magic and bad spirits. Provides +15 protection against sanity damage. Also boosts Metta Mahaniyom. Made by the powerful Luang Pu PhiBoon (PhiBoon Sae Tan), born during the reign of King Rama 4 in Thailand.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.nangkwak.name</t>
+          <t xml:space="preserve">item.timkp.name</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6385,14 +6375,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nang Kwak</t>
+          <t xml:space="preserve">LP Tim Khun Paen Lode Series, Wat Lahanrai</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.nangkwak.desc</t>
+          <t xml:space="preserve">item.timkp.desc</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6402,14 +6392,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t xml:space="preserve">A small brass Nang Kwak, the beckoning lady, her right hand raised to call the customers in. Shopkeepers keep her facing the door.</t>
+          <t xml:space="preserve">Made by the renowned LP Tim Issariko of Wat Lahanrai, this amulet is imbued with the powers from its Phong Prai Kuman powder, granting the wearer prosperity and enhancing charm. Reduce all kinds of damage from minigame events by 50%.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.takrut.name</t>
+          <t xml:space="preserve">item.nangkwak.name</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6419,14 +6409,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takrut</t>
+          <t xml:space="preserve">Nang Kwak</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.takrut.desc</t>
+          <t xml:space="preserve">item.nangkwak.desc</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6436,14 +6426,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t xml:space="preserve">A tiny scroll of metal, a yant inscribed on it and rolled tight, on a cord. It is worn: at the waist, or round the neck.</t>
+          <t xml:space="preserve">A small brass Nang Kwak, the beckoning lady, her right hand raised to call the customers in. Shopkeepers keep her facing the door.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.phayant.name</t>
+          <t xml:space="preserve">item.takrut.name</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6453,14 +6443,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pha yant</t>
+          <t xml:space="preserve">Takrut</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.phayant.desc</t>
+          <t xml:space="preserve">item.takrut.desc</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6470,14 +6460,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t xml:space="preserve">A square of cloth printed with a yant for trade. It is framed on the wall facing the door, below the Buddha shelf.</t>
+          <t xml:space="preserve">A tiny scroll of metal, a yant inscribed on it and rolled tight, on a cord. It is worn: at the waist, or round the neck.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantgaoyord.name</t>
+          <t xml:space="preserve">item.phayant.name</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6487,14 +6477,14 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yant Gao Yord</t>
+          <t xml:space="preserve">Pha yant</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantgaoyord.power</t>
+          <t xml:space="preserve">item.phayant.desc</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6504,14 +6494,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sudden sanity hits reduced by 40%</t>
+          <t xml:space="preserve">A square of cloth printed with a yant for trade. It is framed on the wall facing the door, below the Buddha shelf.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantgaoyord.desc</t>
+          <t xml:space="preserve">item.yantgaoyord.name</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6521,14 +6511,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Nine Spires: the nine peaks of Mount Meru, home of the gods, and the nine qualities of the Buddha, each spire crowned with the three ovals that stand for him. Inked at the top of the back, it protects against weapons, danger, evil spirits and black magic.</t>
+          <t xml:space="preserve">Yant Gao Yord</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yanthahtaew.name</t>
+          <t xml:space="preserve">item.yantgaoyord.power</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6538,14 +6528,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yant Hah Taew Chat Petch</t>
+          <t xml:space="preserve">Sudden sanity hits reduced by 40%</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yanthahtaew.power</t>
+          <t xml:space="preserve">item.yantgaoyord.desc</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6555,14 +6545,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sanity drains 35% slower</t>
+          <t xml:space="preserve">The Nine Spires: the nine peaks of Mount Meru, home of the gods, and the nine qualities of the Buddha, each spire crowned with the three ovals that stand for him. Inked at the top of the back, it protects against weapons, danger, evil spirits and black magic.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yanthahtaew.desc</t>
+          <t xml:space="preserve">item.yanthahtaew.name</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6572,14 +6562,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Five Rows with the Diamond Canopy. Each row is a blessing: protection of the home, help through bad luck, protection from black magic and spirits, good fortune and success, and Metta Mahaniyom, loving kindness and charisma. The Chat Petch adds prosperity and support through difficult periods.</t>
+          <t xml:space="preserve">Yant Hah Taew Chat Petch</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantsroi.name</t>
+          <t xml:space="preserve">item.yanthahtaew.power</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6589,14 +6579,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yant Sroi Sangwan</t>
+          <t xml:space="preserve">Sanity drains 35% slower</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantsroi.power</t>
+          <t xml:space="preserve">item.yanthahtaew.desc</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6606,14 +6596,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minigame damage reduced by 30%</t>
+          <t xml:space="preserve">The Five Rows with the Diamond Canopy. Each row is a blessing: protection of the home, help through bad luck, protection from black magic and spirits, good fortune and success, and Metta Mahaniyom, loving kindness and charisma. The Chat Petch adds prosperity and support through difficult periods.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t xml:space="preserve">item.yantsroi.desc</t>
+          <t xml:space="preserve">item.yantsroi.name</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6623,82 +6613,82 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t xml:space="preserve">A sacred ornament of script worn like a necklace, close to the body. For prosperity, good luck and protection, the strength to overcome obstacles, charm and respect, and a sense of security and inner power.</t>
+          <t xml:space="preserve">Yant Sroi Sangwan</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.wardLeft</t>
+          <t xml:space="preserve">item.yantsroi.power</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel</t>
+          <t xml:space="preserve">Equipment panel — the items</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t xml:space="preserve">{n}/{max} Protection</t>
+          <t xml:space="preserve">Minigame damage reduced by 30%</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t xml:space="preserve">inv.wardSpent</t>
+          <t xml:space="preserve">item.yantsroi.desc</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel</t>
+          <t xml:space="preserve">Equipment panel — the items</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken · recharges next episode</t>
+          <t xml:space="preserve">A sacred ornament of script worn like a necklace, close to the body. For prosperity, good luck and protection, the strength to overcome obstacles, charm and respect, and a sense of security and inner power.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t xml:space="preserve">rarity.common</t>
+          <t xml:space="preserve">inv.wardLeft</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — an item's rarity, under its name (v14.11)</t>
+          <t xml:space="preserve">Equipment panel</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common</t>
+          <t xml:space="preserve">{n}/{max} Protection</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t xml:space="preserve">rarity.rare</t>
+          <t xml:space="preserve">inv.wardSpent</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment panel — an item's rarity, under its name (v14.11)</t>
+          <t xml:space="preserve">Equipment panel</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Broken · recharges next episode</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t xml:space="preserve">rarity.ultrarare</t>
+          <t xml:space="preserve">rarity.common</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6708,48 +6698,48 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultra Rare</t>
+          <t xml:space="preserve">Common</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t xml:space="preserve">unlock.label</t>
+          <t xml:space="preserve">rarity.rare</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ITEM UNLOCKED splash (v14.7)</t>
+          <t xml:space="preserve">Equipment panel — an item's rarity, under its name (v14.11)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item unlocked</t>
+          <t xml:space="preserve">Rare</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t xml:space="preserve">unlock.sub</t>
+          <t xml:space="preserve">rarity.ultrarare</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ITEM UNLOCKED splash (v14.7)</t>
+          <t xml:space="preserve">Equipment panel — an item's rarity, under its name (v14.11)</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added to your bag</t>
+          <t xml:space="preserve">Ultra Rare</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t xml:space="preserve">unlock.close</t>
+          <t xml:space="preserve">unlock.label</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6759,120 +6749,120 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Item unlocked</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t xml:space="preserve">choose.label</t>
+          <t xml:space="preserve">unlock.sub</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ITEM UNLOCKED splash (v14.7)</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choose one</t>
+          <t xml:space="preserve">Added to your bag</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t xml:space="preserve">choose.confirm</t>
+          <t xml:space="preserve">unlock.close</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ITEM UNLOCKED splash (v14.7)</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirm</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t xml:space="preserve">choose.hint</t>
+          <t xml:space="preserve">choose.label</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick one, then confirm</t>
+          <t xml:space="preserve">Choose one</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t xml:space="preserve">ledger.hint</t>
+          <t xml:space="preserve">choose.confirm</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap what you will write</t>
+          <t xml:space="preserve">Confirm</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t xml:space="preserve">ledger.hintKey</t>
+          <t xml:space="preserve">choose.hint</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Click what you will write, or press 1 or 2</t>
+          <t xml:space="preserve">Pick one, then confirm</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t xml:space="preserve">ledger.close</t>
+          <t xml:space="preserve">ledger.hint</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap to close the book</t>
+          <t xml:space="preserve">Tap what you will write</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.label</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The gallery window — pages to turn, a picture and its story (v21.10)</t>
+          <t xml:space="preserve">ledger.hintKey</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gallery</t>
+          <t xml:space="preserve">Click what you will write, or press 1 or 2</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.lived</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The gallery window — pages to turn, a picture and its story (v21.10)</t>
+          <t xml:space="preserve">ledger.close</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lived</t>
+          <t xml:space="preserve">Tap to close the book</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.era</t>
+          <t xml:space="preserve">gallery.label</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6882,14 +6872,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Era</t>
+          <t xml:space="preserve">Gallery</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.temple</t>
+          <t xml:space="preserve">gallery.lived</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6899,14 +6889,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temple</t>
+          <t xml:space="preserve">Lived</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.known</t>
+          <t xml:space="preserve">gallery.era</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6916,14 +6906,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Known for</t>
+          <t xml:space="preserve">Era</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.read</t>
+          <t xml:space="preserve">gallery.temple</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6933,14 +6923,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t xml:space="preserve">{n} of {m} read</t>
+          <t xml:space="preserve">Temple</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.allRead</t>
+          <t xml:space="preserve">gallery.known</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6950,14 +6940,14 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t xml:space="preserve">All {m} read</t>
+          <t xml:space="preserve">Known for</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.nextBtn</t>
+          <t xml:space="preserve">gallery.read</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6967,14 +6957,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next</t>
+          <t xml:space="preserve">{n} of {m} read</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.finish</t>
+          <t xml:space="preserve">gallery.allRead</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6984,14 +6974,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close gallery</t>
+          <t xml:space="preserve">All {m} read</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.prev</t>
+          <t xml:space="preserve">gallery.nextBtn</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -7001,14 +6991,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Previous</t>
+          <t xml:space="preserve">Next</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.next</t>
+          <t xml:space="preserve">gallery.finish</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7018,14 +7008,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next</t>
+          <t xml:space="preserve">Close gallery</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.hint</t>
+          <t xml:space="preserve">gallery.prev</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -7035,14 +7025,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read each story to its end, then tap Next</t>
+          <t xml:space="preserve">Previous</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.hintKey</t>
+          <t xml:space="preserve">gallery.next</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7052,14 +7042,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read each story to its end, then press Next</t>
+          <t xml:space="preserve">Next</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.lockRead</t>
+          <t xml:space="preserve">gallery.hint</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7069,14 +7059,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep reading — Next fills up as you read</t>
+          <t xml:space="preserve">Read each story to its end, then tap Next</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.lockReadLast</t>
+          <t xml:space="preserve">gallery.hintKey</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7086,14 +7076,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep reading — Close gallery fills up as you read</t>
+          <t xml:space="preserve">Read each story to its end, then press Next</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.lockOrder</t>
+          <t xml:space="preserve">gallery.lockRead</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7103,14 +7093,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pages open in order, one at a time</t>
+          <t xml:space="preserve">Keep reading — Next fills up as you read</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.lockStay</t>
+          <t xml:space="preserve">gallery.lockReadLast</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -7120,14 +7110,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t xml:space="preserve">The gallery closes at the end, once every story is read</t>
+          <t xml:space="preserve">Keep reading — Close gallery fills up as you read</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.endNext</t>
+          <t xml:space="preserve">gallery.lockOrder</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -7137,14 +7127,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next</t>
+          <t xml:space="preserve">The pages open in order, one at a time</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.endPull</t>
+          <t xml:space="preserve">gallery.lockStay</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7154,14 +7144,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scroll on to turn the page</t>
+          <t xml:space="preserve">The gallery closes at the end, once every story is read</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.endWait</t>
+          <t xml:space="preserve">gallery.endNext</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -7171,14 +7161,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fills up as you read</t>
+          <t xml:space="preserve">Next</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallery.endFinish</t>
+          <t xml:space="preserve">gallery.endPull</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -7188,58 +7178,48 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close the gallery</t>
+          <t xml:space="preserve">Scroll on to turn the page</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11y.soundButton</t>
+          <t xml:space="preserve">gallery.endWait</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Screen readers only</t>
+          <t xml:space="preserve">The gallery window — pages to turn, a picture and its story (v21.10)</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound on or off</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Never seen on screen</t>
+          <t xml:space="preserve">Fills up as you read</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11y.volumeSlider</t>
+          <t xml:space="preserve">gallery.endFinish</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Screen readers only</t>
+          <t xml:space="preserve">The gallery window — pages to turn, a picture and its story (v21.10)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Game volume</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Never seen on screen</t>
+          <t xml:space="preserve">Close the gallery</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11y.closeButton</t>
+          <t xml:space="preserve">a11y.soundButton</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7249,7 +7229,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Sound on or off</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -7261,7 +7241,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11y.creditsButton</t>
+          <t xml:space="preserve">a11y.volumeSlider</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -7271,7 +7251,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credits</t>
+          <t xml:space="preserve">Game volume</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -7283,20 +7263,64 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
+          <t xml:space="preserve">a11y.closeButton</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screen readers only</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Never seen on screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a11y.creditsButton</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screen readers only</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credits</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Never seen on screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
           <t xml:space="preserve">a11y.menuButton</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t xml:space="preserve">Screen readers only</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t xml:space="preserve">Menu</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t xml:space="preserve">Never seen on screen</t>
         </is>
@@ -21125,7 +21149,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">What changed?</t>
+          <t xml:space="preserve">The storm</t>
         </is>
       </c>
     </row>
@@ -41130,7 +41154,7 @@
         </is>
       </c>
       <c r="F639">
-        <v>7.19</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="640">
@@ -41160,7 +41184,7 @@
         </is>
       </c>
       <c r="F640">
-        <v>8.84</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="641">
@@ -41190,7 +41214,7 @@
         </is>
       </c>
       <c r="F641">
-        <v>7.12</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="642">
@@ -41220,7 +41244,7 @@
         </is>
       </c>
       <c r="F642">
-        <v>5.83</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="643">
@@ -41250,7 +41274,7 @@
         </is>
       </c>
       <c r="F643">
-        <v>5.97</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="644">
@@ -41280,7 +41304,7 @@
         </is>
       </c>
       <c r="F644">
-        <v>4.61</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="645">
@@ -41310,7 +41334,7 @@
         </is>
       </c>
       <c r="F645">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="646">
@@ -41340,7 +41364,7 @@
         </is>
       </c>
       <c r="F646">
-        <v>4.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -41370,7 +41394,7 @@
         </is>
       </c>
       <c r="F647">
-        <v>6.43</v>
+        <v>7.6</v>
       </c>
       <c r="G647" t="inlineStr">
         <is>
@@ -41405,7 +41429,7 @@
         </is>
       </c>
       <c r="F648">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="649">
@@ -41435,7 +41459,7 @@
         </is>
       </c>
       <c r="F649">
-        <v>6.18</v>
+        <v>6.41</v>
       </c>
       <c r="G649" t="inlineStr">
         <is>
@@ -41470,7 +41494,7 @@
         </is>
       </c>
       <c r="F650">
-        <v>1.6</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="651">
@@ -41500,7 +41524,7 @@
         </is>
       </c>
       <c r="F651">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="G651" t="inlineStr">
         <is>
@@ -41535,7 +41559,7 @@
         </is>
       </c>
       <c r="F652">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="G652" t="inlineStr">
         <is>
@@ -41570,7 +41594,7 @@
         </is>
       </c>
       <c r="F653">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="G653" t="inlineStr">
         <is>
@@ -41605,7 +41629,7 @@
         </is>
       </c>
       <c r="F654">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="G654" t="inlineStr">
         <is>
@@ -41640,7 +41664,7 @@
         </is>
       </c>
       <c r="F655">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="G655" t="inlineStr">
         <is>
@@ -41675,7 +41699,7 @@
         </is>
       </c>
       <c r="F656">
-        <v>3.84</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="657">
@@ -41705,7 +41729,7 @@
         </is>
       </c>
       <c r="F657">
-        <v>8.41</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="658">
@@ -41735,7 +41759,7 @@
         </is>
       </c>
       <c r="F658">
-        <v>2.76</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="659">
@@ -41765,7 +41789,7 @@
         </is>
       </c>
       <c r="F659">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="660">
@@ -41795,7 +41819,7 @@
         </is>
       </c>
       <c r="F660">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="661">
@@ -41821,11 +41845,11 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t xml:space="preserve">[cheerful] Ah, you also not from here, right? I'm from KL. My friend recommend. His friend's business — after one visit, double!</t>
+          <t xml:space="preserve">[cheerful] Ah, you're also not from here, right? I'm from KL. My friend recommend. His friend's business — after one visit, double!</t>
         </is>
       </c>
       <c r="F661">
-        <v>8.99</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="662">
@@ -41855,7 +41879,7 @@
         </is>
       </c>
       <c r="F662">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="663">
@@ -41885,7 +41909,7 @@
         </is>
       </c>
       <c r="F663">
-        <v>5.47</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="664">
@@ -41915,7 +41939,7 @@
         </is>
       </c>
       <c r="F664">
-        <v>4.68</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="665">
@@ -41945,7 +41969,7 @@
         </is>
       </c>
       <c r="F665">
-        <v>4.59</v>
+        <v>2.97</v>
       </c>
       <c r="G665" t="inlineStr">
         <is>
@@ -41980,7 +42004,7 @@
         </is>
       </c>
       <c r="F666">
-        <v>8.95</v>
+        <v>8.59</v>
       </c>
       <c r="G666" t="inlineStr">
         <is>
@@ -42015,7 +42039,7 @@
         </is>
       </c>
       <c r="F667">
-        <v>8.86</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="668">
@@ -42045,7 +42069,7 @@
         </is>
       </c>
       <c r="F668">
-        <v>3.84</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="669">
@@ -42075,7 +42099,7 @@
         </is>
       </c>
       <c r="F669">
-        <v>7.52</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="670">
@@ -42105,7 +42129,7 @@
         </is>
       </c>
       <c r="F670">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="671">
@@ -42135,7 +42159,7 @@
         </is>
       </c>
       <c r="F671">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="672">
@@ -42165,7 +42189,7 @@
         </is>
       </c>
       <c r="F672">
-        <v>2.96</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="673">
@@ -42195,7 +42219,7 @@
         </is>
       </c>
       <c r="F673">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="674">
@@ -42225,7 +42249,7 @@
         </is>
       </c>
       <c r="F674">
-        <v>3.21</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="675">
@@ -42255,7 +42279,7 @@
         </is>
       </c>
       <c r="F675">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="676">
@@ -42285,7 +42309,7 @@
         </is>
       </c>
       <c r="F676">
-        <v>4.88</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="677">
@@ -42315,7 +42339,7 @@
         </is>
       </c>
       <c r="F677">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="G677" t="inlineStr">
         <is>
@@ -42350,7 +42374,7 @@
         </is>
       </c>
       <c r="F678">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="679">
@@ -42380,7 +42404,7 @@
         </is>
       </c>
       <c r="F679">
-        <v>2.07</v>
+        <v>1.25</v>
       </c>
       <c r="G679" t="inlineStr">
         <is>
@@ -42415,7 +42439,7 @@
         </is>
       </c>
       <c r="F680">
-        <v>2.76</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="681">
@@ -42445,7 +42469,7 @@
         </is>
       </c>
       <c r="F681">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="682">
@@ -42475,7 +42499,7 @@
         </is>
       </c>
       <c r="F682">
-        <v>4.34</v>
+        <v>2.97</v>
       </c>
       <c r="G682" t="inlineStr">
         <is>
@@ -42510,7 +42534,7 @@
         </is>
       </c>
       <c r="F683">
-        <v>5.22</v>
+        <v>4.49</v>
       </c>
       <c r="G683" t="inlineStr">
         <is>
@@ -42545,7 +42569,7 @@
         </is>
       </c>
       <c r="F684">
-        <v>5.9</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="685">
@@ -42575,7 +42599,7 @@
         </is>
       </c>
       <c r="F685">
-        <v>1.61</v>
+        <v>1.13</v>
       </c>
       <c r="G685" t="inlineStr">
         <is>
@@ -42610,7 +42634,7 @@
         </is>
       </c>
       <c r="F686">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="687">
@@ -42640,7 +42664,7 @@
         </is>
       </c>
       <c r="F687">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G687" t="inlineStr">
         <is>
@@ -42675,7 +42699,7 @@
         </is>
       </c>
       <c r="F688">
-        <v>15.29</v>
+        <v>10.65</v>
       </c>
       <c r="G688" t="inlineStr">
         <is>
@@ -42710,7 +42734,7 @@
         </is>
       </c>
       <c r="F689">
-        <v>10.4</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="690">
@@ -42740,7 +42764,7 @@
         </is>
       </c>
       <c r="F690">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="691">
@@ -42770,7 +42794,7 @@
         </is>
       </c>
       <c r="F691">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G691" t="inlineStr">
         <is>
@@ -42805,7 +42829,7 @@
         </is>
       </c>
       <c r="F692">
-        <v>4.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="693">
@@ -42835,7 +42859,7 @@
         </is>
       </c>
       <c r="F693">
-        <v>3.43</v>
+        <v>2.25</v>
       </c>
       <c r="G693" t="inlineStr">
         <is>
@@ -42870,7 +42894,7 @@
         </is>
       </c>
       <c r="F694">
-        <v>5.13</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="695">
@@ -42900,7 +42924,7 @@
         </is>
       </c>
       <c r="F695">
-        <v>6.28</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="696">
@@ -42930,7 +42954,7 @@
         </is>
       </c>
       <c r="F696">
-        <v>6.67</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="697">
@@ -42960,7 +42984,7 @@
         </is>
       </c>
       <c r="F697">
-        <v>6.33</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="698">
@@ -42990,7 +43014,7 @@
         </is>
       </c>
       <c r="F698">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="G698" t="inlineStr">
         <is>
@@ -43025,7 +43049,7 @@
         </is>
       </c>
       <c r="F699">
-        <v>2.25</v>
+        <v>3.33</v>
       </c>
       <c r="G699" t="inlineStr">
         <is>
@@ -43060,7 +43084,7 @@
         </is>
       </c>
       <c r="F700">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="701">
@@ -43090,7 +43114,7 @@
         </is>
       </c>
       <c r="F701">
-        <v>28</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="702">
@@ -43120,7 +43144,7 @@
         </is>
       </c>
       <c r="F702">
-        <v>40</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="703">
@@ -43150,7 +43174,7 @@
         </is>
       </c>
       <c r="F703">
-        <v>6.73</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="704">
@@ -43180,7 +43204,7 @@
         </is>
       </c>
       <c r="F704">
-        <v>3.46</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="705">
@@ -43210,7 +43234,7 @@
         </is>
       </c>
       <c r="F705">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="706">
@@ -43240,7 +43264,7 @@
         </is>
       </c>
       <c r="F706">
-        <v>3.98</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="707">
@@ -43270,7 +43294,7 @@
         </is>
       </c>
       <c r="F707">
-        <v>4.81</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="708">
@@ -43300,7 +43324,7 @@
         </is>
       </c>
       <c r="F708">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="G708" t="inlineStr">
         <is>
@@ -43335,7 +43359,7 @@
         </is>
       </c>
       <c r="F709">
-        <v>8.21</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="710">
@@ -43365,7 +43389,7 @@
         </is>
       </c>
       <c r="F710">
-        <v>6.42</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="711">
@@ -43395,7 +43419,7 @@
         </is>
       </c>
       <c r="F711">
-        <v>7.05</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="712">
@@ -43425,7 +43449,7 @@
         </is>
       </c>
       <c r="F712">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="G712" t="inlineStr">
         <is>
@@ -43460,7 +43484,7 @@
         </is>
       </c>
       <c r="F713">
-        <v>2.76</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="714">
@@ -43490,7 +43514,7 @@
         </is>
       </c>
       <c r="F714">
-        <v>7.03</v>
+        <v>6.49</v>
       </c>
       <c r="G714" t="inlineStr">
         <is>
@@ -43525,7 +43549,7 @@
         </is>
       </c>
       <c r="F715">
-        <v>1.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="716">
@@ -43555,7 +43579,7 @@
         </is>
       </c>
       <c r="F716">
-        <v>5.28</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="717">
@@ -43585,7 +43609,7 @@
         </is>
       </c>
       <c r="F717">
-        <v>1.22</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="718">
@@ -43615,7 +43639,7 @@
         </is>
       </c>
       <c r="F718">
-        <v>1.33</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="719">
@@ -43645,7 +43669,7 @@
         </is>
       </c>
       <c r="F719">
-        <v>6.42</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="720">
@@ -43675,7 +43699,7 @@
         </is>
       </c>
       <c r="F720">
-        <v>3.84</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="721">
@@ -43705,7 +43729,7 @@
         </is>
       </c>
       <c r="F721">
-        <v>2.89</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="722">
@@ -43735,7 +43759,7 @@
         </is>
       </c>
       <c r="F722">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="G722" t="inlineStr">
         <is>
@@ -43770,7 +43794,7 @@
         </is>
       </c>
       <c r="F723">
-        <v>5.77</v>
+        <v>3.77</v>
       </c>
       <c r="G723" t="inlineStr">
         <is>
@@ -43805,7 +43829,7 @@
         </is>
       </c>
       <c r="F724">
-        <v>8.27</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="725">
@@ -43835,7 +43859,7 @@
         </is>
       </c>
       <c r="F725">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="G725" t="inlineStr">
         <is>
@@ -43870,7 +43894,7 @@
         </is>
       </c>
       <c r="F726">
-        <v>3.07</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="727">
@@ -43900,7 +43924,7 @@
         </is>
       </c>
       <c r="F727">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="728">
@@ -43930,7 +43954,7 @@
         </is>
       </c>
       <c r="F728">
-        <v>3.52</v>
+        <v>2.57</v>
       </c>
       <c r="G728" t="inlineStr">
         <is>
@@ -43965,7 +43989,7 @@
         </is>
       </c>
       <c r="F729">
-        <v>6.03</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="730">
@@ -43995,7 +44019,7 @@
         </is>
       </c>
       <c r="F730">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="731">
@@ -44025,7 +44049,7 @@
         </is>
       </c>
       <c r="F731">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="732">
@@ -44055,7 +44079,7 @@
         </is>
       </c>
       <c r="F732">
-        <v>4.31</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="733">
@@ -44085,7 +44109,7 @@
         </is>
       </c>
       <c r="F733">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="734">
@@ -44115,7 +44139,7 @@
         </is>
       </c>
       <c r="F734">
-        <v>6.92</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="735">
@@ -44145,7 +44169,7 @@
         </is>
       </c>
       <c r="F735">
-        <v>5.13</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="736">
@@ -44175,7 +44199,7 @@
         </is>
       </c>
       <c r="F736">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="737">
@@ -44205,7 +44229,7 @@
         </is>
       </c>
       <c r="F737">
-        <v>3.31</v>
+        <v>2.09</v>
       </c>
       <c r="G737" t="inlineStr">
         <is>
@@ -44240,7 +44264,7 @@
         </is>
       </c>
       <c r="F738">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="G738" t="inlineStr">
         <is>
@@ -44275,7 +44299,7 @@
         </is>
       </c>
       <c r="F739">
-        <v>4.04</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="740">
@@ -44305,7 +44329,7 @@
         </is>
       </c>
       <c r="F740">
-        <v>5.36</v>
+        <v>6.03</v>
       </c>
       <c r="G740" t="inlineStr">
         <is>
@@ -44340,7 +44364,7 @@
         </is>
       </c>
       <c r="F741">
-        <v>3.73</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="742">
@@ -44370,7 +44394,7 @@
         </is>
       </c>
       <c r="F742">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="743">
@@ -44400,7 +44424,7 @@
         </is>
       </c>
       <c r="F743">
-        <v>6.03</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="744">
@@ -44430,7 +44454,7 @@
         </is>
       </c>
       <c r="F744">
-        <v>5.97</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="745">
@@ -44460,7 +44484,7 @@
         </is>
       </c>
       <c r="F745">
-        <v>4.89</v>
+        <v>3.87</v>
       </c>
       <c r="G745" t="inlineStr">
         <is>
@@ -44495,7 +44519,7 @@
         </is>
       </c>
       <c r="F746">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="G746" t="inlineStr">
         <is>
@@ -44530,7 +44554,7 @@
         </is>
       </c>
       <c r="F747">
-        <v>4.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="748">
@@ -44560,7 +44584,7 @@
         </is>
       </c>
       <c r="F748">
-        <v>5.08</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="749">
@@ -44590,7 +44614,7 @@
         </is>
       </c>
       <c r="F749">
-        <v>5.38</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="750">
@@ -44620,7 +44644,7 @@
         </is>
       </c>
       <c r="F750">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="751">
@@ -44650,7 +44674,7 @@
         </is>
       </c>
       <c r="F751">
-        <v>3.53</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="752">
@@ -44680,7 +44704,7 @@
         </is>
       </c>
       <c r="F752">
-        <v>5.45</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="753">
@@ -44710,7 +44734,7 @@
         </is>
       </c>
       <c r="F753">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="754">
@@ -44740,7 +44764,7 @@
         </is>
       </c>
       <c r="F754">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="755">
@@ -44770,7 +44794,7 @@
         </is>
       </c>
       <c r="F755">
-        <v>3.26</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="756">
@@ -44800,7 +44824,7 @@
         </is>
       </c>
       <c r="F756">
-        <v>2.87</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="757">
@@ -44830,7 +44854,7 @@
         </is>
       </c>
       <c r="F757">
-        <v>6.22</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="758">
@@ -44860,7 +44884,7 @@
         </is>
       </c>
       <c r="F758">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="759">
@@ -44890,7 +44914,7 @@
         </is>
       </c>
       <c r="F759">
-        <v>4.68</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="760">
@@ -44920,7 +44944,7 @@
         </is>
       </c>
       <c r="F760">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
